--- a/artfynd/A 16233-2020 artfynd.xlsx
+++ b/artfynd/A 16233-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 16233-2020 artfynd.xlsx
+++ b/artfynd/A 16233-2020 artfynd.xlsx
@@ -1722,10 +1722,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120008974</v>
+        <v>120008942</v>
       </c>
       <c r="B11" t="n">
-        <v>90846</v>
+        <v>91005</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1734,25 +1734,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1828,10 +1828,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120008942</v>
+        <v>120008974</v>
       </c>
       <c r="B12" t="n">
-        <v>91005</v>
+        <v>90846</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1840,25 +1840,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>

--- a/artfynd/A 16233-2020 artfynd.xlsx
+++ b/artfynd/A 16233-2020 artfynd.xlsx
@@ -1725,7 +1725,7 @@
         <v>120008942</v>
       </c>
       <c r="B11" t="n">
-        <v>91005</v>
+        <v>91023</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
         <v>120008974</v>
       </c>
       <c r="B12" t="n">
-        <v>90846</v>
+        <v>90864</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>

--- a/artfynd/A 16233-2020 artfynd.xlsx
+++ b/artfynd/A 16233-2020 artfynd.xlsx
@@ -1722,10 +1722,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120008942</v>
+        <v>120008974</v>
       </c>
       <c r="B11" t="n">
-        <v>91023</v>
+        <v>90864</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1734,25 +1734,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1828,10 +1828,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120008974</v>
+        <v>120008942</v>
       </c>
       <c r="B12" t="n">
-        <v>90864</v>
+        <v>91023</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1840,25 +1840,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>

--- a/artfynd/A 16233-2020 artfynd.xlsx
+++ b/artfynd/A 16233-2020 artfynd.xlsx
@@ -1722,10 +1722,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120008974</v>
+        <v>120008942</v>
       </c>
       <c r="B11" t="n">
-        <v>90864</v>
+        <v>91023</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1734,25 +1734,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1828,10 +1828,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120008942</v>
+        <v>120008974</v>
       </c>
       <c r="B12" t="n">
-        <v>91023</v>
+        <v>90864</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1840,25 +1840,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
